--- a/株式会社チェングロウス御中_LINEOA施策提案【SIM】.xlsx
+++ b/株式会社チェングロウス御中_LINEOA施策提案【SIM】.xlsx
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="E36" s="111" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="111" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="111" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" s="111" t="n">
+        <v>17</v>
+      </c>
+      <c r="I36" s="111" t="n">
+        <v>21</v>
+      </c>
+      <c r="J36" s="111" t="n">
         <v>25</v>
-      </c>
-      <c r="F36" s="111" t="n">
-        <v>30</v>
-      </c>
-      <c r="G36" s="111" t="n">
-        <v>33</v>
-      </c>
-      <c r="H36" s="111" t="n">
-        <v>35</v>
-      </c>
-      <c r="I36" s="111" t="n">
-        <v>36</v>
-      </c>
-      <c r="J36" s="111" t="n">
-        <v>37</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
@@ -6070,22 +6070,22 @@
         <v>0</v>
       </c>
       <c r="E36" s="111" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="F36" s="111" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="G36" s="111" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="H36" s="111" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="I36" s="111" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J36" s="111" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>

--- a/株式会社チェングロウス御中_LINEOA施策提案【SIM】.xlsx
+++ b/株式会社チェングロウス御中_LINEOA施策提案【SIM】.xlsx
@@ -2342,22 +2342,22 @@
         </is>
       </c>
       <c r="E22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="F22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="G22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="H22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="I22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="J22" s="63" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
       <c r="K22" s="11" t="n"/>
       <c r="L22" s="7" t="n"/>
@@ -2816,7 +2816,9 @@
           <t>CPFの単価設定</t>
         </is>
       </c>
-      <c r="P30" s="172" t="n"/>
+      <c r="P30" s="172" t="n">
+        <v>300</v>
+      </c>
       <c r="S30" s="34" t="n"/>
       <c r="U30" s="34" t="n"/>
       <c r="W30" s="34" t="n"/>
@@ -3090,19 +3092,19 @@
         <v>5</v>
       </c>
       <c r="F36" s="111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" s="111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H36" s="111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" s="111" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J36" s="111" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
